--- a/sampleprojects/TaxReturn/excel/states/KY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/KY.xlsx
@@ -87,7 +87,7 @@
     <t>Compute KY taxable income (AGI − $3,270) and 4.00% tax</t>
   </si>
   <si>
-    <t>set result.ky_taxable_income = the maximum of (result.agi - ky_standard_deduction) and 0.0; set result.ky_state_tax = result.ky_taxable_income * ky_tax_rate; add "  KY taxable income (AGI - $3,270): $" + result.ky_taxable_income to job.audit_trail; add "  KY state tax (4.00%): $" + result.ky_state_tax to job.audit_trail</t>
+    <t>set result.ky_taxable_income = the maximum of (result.state_calc_agi - ky_standard_deduction) and 0.0; set result.ky_state_tax = result.ky_taxable_income * ky_tax_rate; add "  KY taxable income (AGI - $3,270): $" + result.ky_taxable_income to job.audit_trail; add "  KY state tax (4.00%): $" + result.ky_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>

--- a/sampleprojects/TaxReturn/excel/states/KY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/KY.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>DT: ky military retirement exemption</t>
   </si>
@@ -36,6 +36,12 @@
     <t>DSL: CONTEXTS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
     <t>INITIAL ACTIONS: COMMENTS</t>
   </si>
   <si>
@@ -48,19 +54,43 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
+    <t>The taxpayer has military retired pay, a federal pension (Form 740 packet: Federal and Military Retirement Systems, taxable, Schedule P)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>ACTIONS: COMMENTS</t>
   </si>
   <si>
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>No military retirement pay</t>
-  </si>
-  <si>
-    <t>/* No military retirement pay - no exemption. */</t>
-  </si>
-  <si>
-    <t/>
+    <t>Schedule M line 9 / Schedule P Part II: 100% of taxable retirement benefits or $31,110, whichever is less, per taxpayer (KRS 141.019(1)(g)1.b)</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and ky_pension_exclusion to result.ky_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Kentucky has no military-specific exemption; military retired pay for service after 1997 takes the general pension income exclusion, the lesser of the pay and $31,110 per taxpayer (Schedule M line 9; Schedule P Part II line 3; KRS 141.019(1)(g)1.b; 2025 Form 740 packet). Service credit before 1998 would be exempt in full on Schedule P Part I and is not modelled.</t>
+  </si>
+  <si>
+    <t>No military retired pay for this taxpayer.</t>
   </si>
   <si>
     <t>DT: KY Tax</t>
@@ -72,7 +102,7 @@
     <t>TABLE_NUMBER: 41800</t>
   </si>
   <si>
-    <t>set result.ky_state_tax = 0; set result.ky_taxable_income = 0; add "  Kentucky Tax Calculation (Form 740) - flat 4.00%" to job.audit_trail</t>
+    <t>set result.ky_state_tax = 0; set result.ky_taxable_income = 0; add "  Kentucky Tax Calculation (Form 740) - flat 4.00%" to job.audit_trail; set result.ky_military_retirement_exemption = 0.0; perform ky_military_retirement_exemption; add "  KY Schedule M line 9 pension income exclusion (military retired pay): $" + result.ky_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>Always compute (single-column FIRST table; deduction is uniform)</t>
@@ -81,16 +111,10 @@
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Compute KY taxable income (AGI − $3,270) and 4.00% tax</t>
-  </si>
-  <si>
-    <t>set result.ky_taxable_income = the maximum of (result.state_calc_agi - ky_standard_deduction) and 0.0; set result.ky_state_tax = result.ky_taxable_income * ky_tax_rate; add "  KY taxable income (AGI - $3,270): $" + result.ky_taxable_income to job.audit_trail; add "  KY state tax (4.00%): $" + result.ky_state_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>Form 740: Kentucky AGI (line 9) is federal AGI less Schedule M subtractions, here the pension income exclusion; less the $3,270 standard deduction (line 10); tax 4% (line 12)</t>
+  </si>
+  <si>
+    <t>set result.ky_taxable_income = the maximum of (result.state_calc_agi - result.ky_military_retirement_exemption - ky_standard_deduction) and 0.0; set result.ky_state_tax = result.ky_taxable_income * ky_tax_rate; add "  KY taxable income (AGI - $3,270): $" + result.ky_taxable_income to job.audit_trail; add "  KY state tax (4.00%): $" + result.ky_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -99,13 +123,7 @@
     <t>set result.computed_state_taxable_income = result.ky_taxable_income; set result.computed_state_tax = result.ky_state_tax</t>
   </si>
   <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>KY flat tax: 4.00% × max(AGI − $3,270, 0)</t>
+    <t>KY flat tax: 4.00% x max(AGI - pension income exclusion (Schedule M line 9, up to $31,110 per taxpayer, applied to military retired pay) - $3,270, 0).</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -168,7 +186,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>KY military retirement exemption (computed)</t>
+    <t>KY pension income exclusion applied to military retired pay (computed per taxpayer by ky_military_retirement_exemption): the lesser of the pay and $31,110 (Schedule M line 9, KRS 141.019(1)(g)1.b) (#1330).</t>
   </si>
   <si>
     <t>ky_military_retirement_exemption_amount</t>
@@ -177,7 +195,7 @@
     <t>31110.0</t>
   </si>
   <si>
-    <t>KY military retirement exemption - $31,110 (2025). Source: MOAA</t>
+    <t>Kentucky has no military-specific exemption: military retired pay for service after 1997 is a federal pension under the general pension income exclusion, 100% of taxable retirement benefits or $31,110 per taxpayer, whichever is less (Schedule M line 9; Schedule P Part II; KRS 141.019(1)(g)1.b; 2025 Form 740 packet). Equals ky_pension_exclusion, which the rules read. Service credit earned before 1998 is excluded in full on Schedule P Part I and is not modelled (#1330).</t>
   </si>
   <si>
     <t>ky_military_retirement_taxable</t>
@@ -796,216 +814,479 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K11" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="N14" s="4">
         <v>11</v>
       </c>
-      <c r="D12" s="4">
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F17" s="1">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G17" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H17" s="1">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
-        <v>6</v>
-      </c>
-      <c r="J12" s="4">
+      <c r="I17" s="1">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K17" s="1">
         <v>8</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L17" s="1">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M17" s="1">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N17" s="1">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O17" s="1">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P17" s="1">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q17" s="1">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R17" s="1">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S17" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5">
+    <row r="18">
+      <c r="A18" s="5">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>14</v>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1021,7 +1302,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1067,7 +1348,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1090,7 +1371,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1138,11 +1419,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1166,10 +1447,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1190,11 +1471,11 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1250,67 +1531,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1366,58 +1647,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1425,67 +1706,67 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -1541,58 +1822,58 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1633,56 +1914,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1698,330 +1979,330 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/sampleprojects/TaxReturn/excel/states/KY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/KY.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>DT: ky military retirement exemption</t>
   </si>
@@ -66,6 +66,15 @@
     <t>N</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>ACTIONS: COMMENTS</t>
   </si>
   <si>
@@ -91,6 +100,9 @@
   </si>
   <si>
     <t>No military retired pay for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>DT: KY Tax</t>
@@ -940,7 +952,7 @@
         <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>6</v>
@@ -982,294 +994,412 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F15" s="4">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G15" s="4">
         <v>4</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
         <v>7</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K15" s="4">
         <v>8</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L15" s="4">
         <v>9</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M15" s="4">
         <v>10</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N15" s="4">
         <v>11</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O15" s="4">
         <v>12</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P15" s="4">
         <v>13</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q15" s="4">
         <v>14</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R15" s="4">
         <v>15</v>
       </c>
-      <c r="S14" s="4">
+      <c r="S15" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5">
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18" s="1">
         <v>3</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H18" s="1">
         <v>5</v>
       </c>
-      <c r="I17" s="1">
-        <v>6</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
         <v>7</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K18" s="1">
         <v>8</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L18" s="1">
         <v>9</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M18" s="1">
         <v>10</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N18" s="1">
         <v>11</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P18" s="1">
         <v>13</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q18" s="1">
         <v>14</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R18" s="1">
         <v>15</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S18" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>2</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1285,8 +1415,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1302,7 +1432,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1348,7 +1478,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1371,7 +1501,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1450,7 +1580,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1531,10 +1661,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -1587,11 +1717,11 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1647,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1706,13 +1836,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1762,11 +1892,11 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -1822,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>6</v>
@@ -1914,56 +2044,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1982,25 +2112,25 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>6</v>
@@ -2023,25 +2153,25 @@
         <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="D5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>6</v>
@@ -2064,25 +2194,25 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>6</v>
@@ -2105,25 +2235,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>6</v>
@@ -2146,25 +2276,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>6</v>
@@ -2187,25 +2317,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>6</v>
@@ -2228,25 +2358,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>6</v>
@@ -2269,25 +2399,25 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>6</v>

--- a/sampleprojects/TaxReturn/excel/states/KY.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/KY.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>DT: ky military retirement exemption</t>
   </si>
@@ -36,6 +36,12 @@
     <t>DSL: CONTEXTS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
     <t>INITIAL ACTIONS: COMMENTS</t>
   </si>
   <si>
@@ -48,19 +54,55 @@
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
+    <t>The taxpayer has military retired pay, a federal pension (Form 740 packet: Federal and Military Retirement Systems, taxable, Schedule P)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>ACTIONS: COMMENTS</t>
   </si>
   <si>
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>No military retirement pay</t>
-  </si>
-  <si>
-    <t>/* No military retirement pay - no exemption. */</t>
-  </si>
-  <si>
-    <t/>
+    <t>Schedule M line 9 / Schedule P Part II: 100% of taxable retirement benefits or $31,110, whichever is less, per taxpayer (KRS 141.019(1)(g)1.b)</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and ky_pension_exclusion to result.ky_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Kentucky has no military-specific exemption; military retired pay for service after 1997 takes the general pension income exclusion, the lesser of the pay and $31,110 per taxpayer (Schedule M line 9; Schedule P Part II line 3; KRS 141.019(1)(g)1.b; 2025 Form 740 packet). Service credit before 1998 would be exempt in full on Schedule P Part I and is not modelled.</t>
+  </si>
+  <si>
+    <t>No military retired pay for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>DT: KY Tax</t>
@@ -72,7 +114,7 @@
     <t>TABLE_NUMBER: 41800</t>
   </si>
   <si>
-    <t>set result.ky_state_tax = 0; set result.ky_taxable_income = 0; add "  Kentucky Tax Calculation (Form 740) - flat 4.00%" to job.audit_trail</t>
+    <t>set result.ky_state_tax = 0; set result.ky_taxable_income = 0; add "  Kentucky Tax Calculation (Form 740) - flat 4.00%" to job.audit_trail; set result.ky_military_retirement_exemption = 0.0; perform ky_military_retirement_exemption; add "  KY Schedule M line 9 pension income exclusion (military retired pay): $" + result.ky_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>Always compute (single-column FIRST table; deduction is uniform)</t>
@@ -81,16 +123,10 @@
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Compute KY taxable income (AGI − $3,270) and 4.00% tax</t>
-  </si>
-  <si>
-    <t>set result.ky_taxable_income = the maximum of (result.state_calc_agi - ky_standard_deduction) and 0.0; set result.ky_state_tax = result.ky_taxable_income * ky_tax_rate; add "  KY taxable income (AGI - $3,270): $" + result.ky_taxable_income to job.audit_trail; add "  KY state tax (4.00%): $" + result.ky_state_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>Form 740: Kentucky AGI (line 9) is federal AGI less Schedule M subtractions, here the pension income exclusion; less the $3,270 standard deduction (line 10); tax 4% (line 12)</t>
+  </si>
+  <si>
+    <t>set result.ky_taxable_income = the maximum of (result.state_calc_agi - result.ky_military_retirement_exemption - ky_standard_deduction) and 0.0; set result.ky_state_tax = result.ky_taxable_income * ky_tax_rate; add "  KY taxable income (AGI - $3,270): $" + result.ky_taxable_income to job.audit_trail; add "  KY state tax (4.00%): $" + result.ky_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -99,13 +135,7 @@
     <t>set result.computed_state_taxable_income = result.ky_taxable_income; set result.computed_state_tax = result.ky_state_tax</t>
   </si>
   <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>KY flat tax: 4.00% × max(AGI − $3,270, 0)</t>
+    <t>KY flat tax: 4.00% x max(AGI - pension income exclusion (Schedule M line 9, up to $31,110 per taxpayer, applied to military retired pay) - $3,270, 0).</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -168,7 +198,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>KY military retirement exemption (computed)</t>
+    <t>KY pension income exclusion applied to military retired pay (computed per taxpayer by ky_military_retirement_exemption): the lesser of the pay and $31,110 (Schedule M line 9, KRS 141.019(1)(g)1.b) (#1330).</t>
   </si>
   <si>
     <t>ky_military_retirement_exemption_amount</t>
@@ -177,7 +207,7 @@
     <t>31110.0</t>
   </si>
   <si>
-    <t>KY military retirement exemption - $31,110 (2025). Source: MOAA</t>
+    <t>Kentucky has no military-specific exemption: military retired pay for service after 1997 is a federal pension under the general pension income exclusion, 100% of taxable retirement benefits or $31,110 per taxpayer, whichever is less (Schedule M line 9; Schedule P Part II; KRS 141.019(1)(g)1.b; 2025 Form 740 packet). Equals ky_pension_exclusion, which the rules read. Service credit earned before 1998 is excluded in full on Schedule P Part I and is not modelled (#1330).</t>
   </si>
   <si>
     <t>ky_military_retirement_taxable</t>
@@ -796,216 +826,597 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K11" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
-      <c r="G12" s="4">
-        <v>4</v>
-      </c>
-      <c r="H12" s="4">
-        <v>5</v>
-      </c>
-      <c r="I12" s="4">
-        <v>6</v>
-      </c>
-      <c r="J12" s="4">
-        <v>7</v>
-      </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
-        <v>9</v>
-      </c>
-      <c r="M12" s="4">
-        <v>10</v>
-      </c>
-      <c r="N12" s="4">
-        <v>11</v>
-      </c>
-      <c r="O12" s="4">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
-        <v>16</v>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
         <v>14</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
+        <v>9</v>
+      </c>
+      <c r="M18" s="1">
+        <v>10</v>
+      </c>
+      <c r="N18" s="1">
+        <v>11</v>
+      </c>
+      <c r="O18" s="1">
+        <v>12</v>
+      </c>
+      <c r="P18" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="1">
         <v>14</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>14</v>
+      <c r="R18" s="1">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1021,7 +1432,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1067,7 +1478,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1090,7 +1501,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1138,11 +1549,11 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1166,10 +1577,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1190,11 +1601,11 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1250,67 +1661,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1366,58 +1777,58 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1425,67 +1836,67 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -1541,58 +1952,58 @@
         <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1633,56 +2044,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1698,330 +2109,330 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="H8" s="16" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
